--- a/1차프로젝트/2. 개발스케줄표_신혜린.xlsx
+++ b/1차프로젝트/2. 개발스케줄표_신혜린.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\Desktop\바탕화면_1차프로젝트\ShinHyerin_1st_Project\1차프로젝트\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCE6F1B9-26C6-4317-8777-8B339EC077DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{461FC5BB-85CC-4B7F-837F-374530A0923E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4389" yWindow="1629" windowWidth="16457" windowHeight="9454" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MLR 웹 서비스 개발 스케줄링" sheetId="1" r:id="rId1"/>
@@ -377,26 +377,26 @@
     <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -631,98 +631,98 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:62" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="27" t="s">
+      <c r="B1" s="31" t="s">
         <v>10</v>
       </c>
-      <c r="C1" s="28" t="s">
+      <c r="C1" s="29" t="s">
         <v>6</v>
       </c>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
-      <c r="H1" s="28"/>
-      <c r="I1" s="28"/>
-      <c r="J1" s="28"/>
-      <c r="K1" s="28"/>
-      <c r="L1" s="28"/>
-      <c r="M1" s="28"/>
-      <c r="N1" s="28"/>
-      <c r="O1" s="28"/>
-      <c r="P1" s="28"/>
-      <c r="Q1" s="28"/>
-      <c r="R1" s="27" t="s">
+      <c r="D1" s="29"/>
+      <c r="E1" s="29"/>
+      <c r="F1" s="29"/>
+      <c r="G1" s="29"/>
+      <c r="H1" s="29"/>
+      <c r="I1" s="29"/>
+      <c r="J1" s="29"/>
+      <c r="K1" s="29"/>
+      <c r="L1" s="29"/>
+      <c r="M1" s="29"/>
+      <c r="N1" s="29"/>
+      <c r="O1" s="29"/>
+      <c r="P1" s="29"/>
+      <c r="Q1" s="29"/>
+      <c r="R1" s="31" t="s">
         <v>7</v>
       </c>
-      <c r="S1" s="28"/>
-      <c r="T1" s="28"/>
-      <c r="U1" s="28"/>
-      <c r="V1" s="28"/>
-      <c r="W1" s="28"/>
-      <c r="X1" s="28"/>
-      <c r="Y1" s="28"/>
-      <c r="Z1" s="28"/>
-      <c r="AA1" s="28"/>
-      <c r="AB1" s="28"/>
-      <c r="AC1" s="28"/>
-      <c r="AD1" s="28"/>
-      <c r="AE1" s="28"/>
-      <c r="AF1" s="28"/>
+      <c r="S1" s="29"/>
+      <c r="T1" s="29"/>
+      <c r="U1" s="29"/>
+      <c r="V1" s="29"/>
+      <c r="W1" s="29"/>
+      <c r="X1" s="29"/>
+      <c r="Y1" s="29"/>
+      <c r="Z1" s="29"/>
+      <c r="AA1" s="29"/>
+      <c r="AB1" s="29"/>
+      <c r="AC1" s="29"/>
+      <c r="AD1" s="29"/>
+      <c r="AE1" s="29"/>
+      <c r="AF1" s="29"/>
       <c r="AG1" s="2"/>
       <c r="AH1" s="2"/>
       <c r="AI1" s="2"/>
-      <c r="AJ1" s="30"/>
-      <c r="AK1" s="31"/>
-      <c r="AL1" s="31"/>
+      <c r="AJ1" s="27"/>
+      <c r="AK1" s="28"/>
+      <c r="AL1" s="28"/>
     </row>
     <row r="2" spans="1:62" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="28"/>
-      <c r="B2" s="28"/>
-      <c r="C2" s="28" t="s">
+      <c r="A2" s="29"/>
+      <c r="B2" s="29"/>
+      <c r="C2" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
-      <c r="F2" s="28"/>
-      <c r="G2" s="28"/>
-      <c r="H2" s="29" t="s">
+      <c r="D2" s="29"/>
+      <c r="E2" s="29"/>
+      <c r="F2" s="29"/>
+      <c r="G2" s="29"/>
+      <c r="H2" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="I2" s="28"/>
-      <c r="J2" s="28"/>
-      <c r="K2" s="28"/>
-      <c r="L2" s="28"/>
-      <c r="M2" s="29" t="s">
+      <c r="I2" s="29"/>
+      <c r="J2" s="29"/>
+      <c r="K2" s="29"/>
+      <c r="L2" s="29"/>
+      <c r="M2" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="N2" s="28"/>
-      <c r="O2" s="28"/>
-      <c r="P2" s="28"/>
-      <c r="Q2" s="28"/>
-      <c r="R2" s="29" t="s">
+      <c r="N2" s="29"/>
+      <c r="O2" s="29"/>
+      <c r="P2" s="29"/>
+      <c r="Q2" s="29"/>
+      <c r="R2" s="30" t="s">
         <v>3</v>
       </c>
-      <c r="S2" s="28"/>
-      <c r="T2" s="28"/>
-      <c r="U2" s="28"/>
-      <c r="V2" s="28"/>
-      <c r="W2" s="29" t="s">
+      <c r="S2" s="29"/>
+      <c r="T2" s="29"/>
+      <c r="U2" s="29"/>
+      <c r="V2" s="29"/>
+      <c r="W2" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="X2" s="28"/>
-      <c r="Y2" s="28"/>
-      <c r="Z2" s="28"/>
-      <c r="AA2" s="28"/>
-      <c r="AB2" s="29" t="s">
+      <c r="X2" s="29"/>
+      <c r="Y2" s="29"/>
+      <c r="Z2" s="29"/>
+      <c r="AA2" s="29"/>
+      <c r="AB2" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="AC2" s="28"/>
-      <c r="AD2" s="28"/>
-      <c r="AE2" s="28"/>
-      <c r="AF2" s="28"/>
+      <c r="AC2" s="29"/>
+      <c r="AD2" s="29"/>
+      <c r="AE2" s="29"/>
+      <c r="AF2" s="29"/>
       <c r="AH2" s="2"/>
       <c r="AI2" s="2"/>
       <c r="AJ2" s="2"/>
@@ -730,7 +730,7 @@
       <c r="AL2" s="2"/>
     </row>
     <row r="3" spans="1:62" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="27" t="s">
+      <c r="A3" s="31" t="s">
         <v>4</v>
       </c>
       <c r="B3" s="16" t="s">
@@ -768,7 +768,7 @@
       <c r="AF3" s="7"/>
     </row>
     <row r="4" spans="1:62" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="27"/>
+      <c r="A4" s="31"/>
       <c r="B4" s="16" t="s">
         <v>11</v>
       </c>
@@ -804,7 +804,7 @@
       <c r="AF4" s="7"/>
     </row>
     <row r="5" spans="1:62" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="27"/>
+      <c r="A5" s="31"/>
       <c r="B5" s="16" t="s">
         <v>5</v>
       </c>
@@ -840,7 +840,7 @@
       <c r="AF5" s="7"/>
     </row>
     <row r="6" spans="1:62" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="27" t="s">
+      <c r="A6" s="31" t="s">
         <v>8</v>
       </c>
       <c r="B6" s="17" t="s">
@@ -878,7 +878,7 @@
       <c r="AF6" s="8"/>
     </row>
     <row r="7" spans="1:62" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="27"/>
+      <c r="A7" s="31"/>
       <c r="B7" s="17" t="s">
         <v>13</v>
       </c>
@@ -894,7 +894,7 @@
       <c r="L7" s="7"/>
       <c r="M7" s="20"/>
       <c r="N7" s="22"/>
-      <c r="O7" s="6"/>
+      <c r="O7" s="7"/>
       <c r="P7" s="7"/>
       <c r="Q7" s="7"/>
       <c r="R7" s="7"/>
@@ -914,7 +914,7 @@
       <c r="AF7" s="8"/>
     </row>
     <row r="8" spans="1:62" s="3" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="27"/>
+      <c r="A8" s="31"/>
       <c r="B8" s="17" t="s">
         <v>29</v>
       </c>
@@ -930,7 +930,7 @@
       <c r="L8" s="7"/>
       <c r="M8" s="20"/>
       <c r="N8" s="22"/>
-      <c r="O8" s="6"/>
+      <c r="O8" s="7"/>
       <c r="P8" s="7"/>
       <c r="Q8" s="7"/>
       <c r="R8" s="7"/>
@@ -950,7 +950,7 @@
       <c r="AF8" s="8"/>
     </row>
     <row r="9" spans="1:62" ht="15.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="28" t="s">
+      <c r="A9" s="29" t="s">
         <v>14</v>
       </c>
       <c r="B9" s="17" t="s">
@@ -967,7 +967,7 @@
       <c r="K9" s="14"/>
       <c r="L9" s="14"/>
       <c r="M9" s="7"/>
-      <c r="N9" s="22"/>
+      <c r="N9" s="20"/>
       <c r="O9" s="22"/>
       <c r="P9" s="7"/>
       <c r="Q9" s="7"/>
@@ -988,7 +988,7 @@
       <c r="AF9" s="8"/>
     </row>
     <row r="10" spans="1:62" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="28"/>
+      <c r="A10" s="29"/>
       <c r="B10" s="17" t="s">
         <v>16</v>
       </c>
@@ -1005,7 +1005,7 @@
       <c r="M10" s="7"/>
       <c r="N10" s="7"/>
       <c r="O10" s="6"/>
-      <c r="P10" s="6"/>
+      <c r="P10" s="7"/>
       <c r="Q10" s="24"/>
       <c r="R10" s="7"/>
       <c r="S10" s="7"/>
@@ -1024,7 +1024,7 @@
       <c r="AF10" s="8"/>
     </row>
     <row r="11" spans="1:62" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="28"/>
+      <c r="A11" s="29"/>
       <c r="B11" s="17" t="s">
         <v>17</v>
       </c>
@@ -1040,7 +1040,7 @@
       <c r="L11" s="14"/>
       <c r="M11" s="7"/>
       <c r="N11" s="7"/>
-      <c r="O11" s="7"/>
+      <c r="O11" s="6"/>
       <c r="P11" s="6"/>
       <c r="Q11" s="6"/>
       <c r="R11" s="7"/>
@@ -1060,10 +1060,10 @@
       <c r="AF11" s="8"/>
     </row>
     <row r="12" spans="1:62" ht="15.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="32" t="s">
+      <c r="A12" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="B12" s="32"/>
+      <c r="B12" s="33"/>
       <c r="C12" s="8"/>
       <c r="D12" s="8"/>
       <c r="E12" s="7"/>
@@ -1096,7 +1096,7 @@
       <c r="AF12" s="8"/>
     </row>
     <row r="13" spans="1:62" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="33" t="s">
+      <c r="A13" s="32" t="s">
         <v>23</v>
       </c>
       <c r="B13" s="16" t="s">
@@ -1164,7 +1164,7 @@
       <c r="BJ13" s="12"/>
     </row>
     <row r="14" spans="1:62" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="33"/>
+      <c r="A14" s="32"/>
       <c r="B14" s="18" t="s">
         <v>19</v>
       </c>
@@ -1230,7 +1230,7 @@
       <c r="BJ14" s="12"/>
     </row>
     <row r="15" spans="1:62" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="33"/>
+      <c r="A15" s="32"/>
       <c r="B15" s="16" t="s">
         <v>20</v>
       </c>
@@ -1296,7 +1296,7 @@
       <c r="BJ15" s="12"/>
     </row>
     <row r="16" spans="1:62" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="33" t="s">
+      <c r="A16" s="32" t="s">
         <v>24</v>
       </c>
       <c r="B16" s="16" t="s">
@@ -1364,7 +1364,7 @@
       <c r="BJ16" s="12"/>
     </row>
     <row r="17" spans="1:32" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="33"/>
+      <c r="A17" s="32"/>
       <c r="B17" s="17" t="s">
         <v>22</v>
       </c>
@@ -1439,23 +1439,23 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="AJ1:AL1"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="H2:L2"/>
-    <mergeCell ref="W2:AA2"/>
-    <mergeCell ref="AB2:AF2"/>
+    <mergeCell ref="A3:A5"/>
+    <mergeCell ref="A13:A15"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="A9:A11"/>
+    <mergeCell ref="A6:A8"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:Q1"/>
     <mergeCell ref="R1:AF1"/>
     <mergeCell ref="M2:Q2"/>
     <mergeCell ref="R2:V2"/>
-    <mergeCell ref="A3:A5"/>
-    <mergeCell ref="A13:A15"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="A9:A11"/>
-    <mergeCell ref="A6:A8"/>
+    <mergeCell ref="AJ1:AL1"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="W2:AA2"/>
+    <mergeCell ref="AB2:AF2"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
